--- a/output/pdf_financials_xlsx/AURO.xlsx
+++ b/output/pdf_financials_xlsx/AURO.xlsx
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.174315</v>
+        <v>-2.174315</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.15374</v>
+        <v>-2.15374</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.448903</v>
+        <v>-4.448903</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.174315</v>
+        <v>-2.174315</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.15374</v>
+        <v>-2.15374</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.448903</v>
+        <v>-4.448903</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.174315</v>
+        <v>-2.174315</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.15374</v>
+        <v>-2.15374</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.448903</v>
+        <v>-4.448903</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>54.357875</v>
+        <v>-54.357875</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>53.8435</v>
+        <v>-53.8435</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>63.555757</v>
+        <v>-63.555757</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.174315</v>
+        <v>-2.174315</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.15374</v>
+        <v>-2.15374</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.448903</v>
+        <v>-4.448903</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.191431</v>
+        <v>-2.157199</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.175498</v>
+        <v>-2.131982</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.472413</v>
+        <v>-4.425393</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.70019</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.838273</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.386847</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.665907</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.873777</v>
       </c>
     </row>
     <row r="93">
@@ -4210,7 +4210,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -5690,7 +5694,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6287,7 +6295,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.70019</v>
       </c>
@@ -9734,10 +9746,10 @@
         </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>2.15374</v>
+        <v>-2.15374</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>4.448903</v>
+        <v>-4.448903</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10141,10 +10153,10 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2.174315</v>
+        <v>-2.174315</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>2.15374</v>
+        <v>-2.15374</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AURO.xlsx
+++ b/output/pdf_financials_xlsx/AURO.xlsx
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.04074</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>-2.15374</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.448903</v>
+        <v>-4.408163</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>-2.131982</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.425393</v>
+        <v>-4.384653</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1278,19 +1278,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.149913</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.061188</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.105428</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.105498</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.085378</v>
       </c>
     </row>
     <row r="35">
@@ -1322,19 +1322,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.149913</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.061188</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.105428</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.105498</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.085378</v>
       </c>
     </row>
     <row r="37">
@@ -1586,19 +1586,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.218706</v>
+        <v>0.06879300000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.197573</v>
+        <v>0.136385</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.207998</v>
+        <v>0.10257</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.182011</v>
+        <v>0.076513</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.092597</v>
+        <v>0.007219</v>
       </c>
     </row>
     <row r="49">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3861,7 +3861,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.015075</v>
       </c>
@@ -9530,7 +9534,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9575,7 +9579,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9981,7 +9985,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">

--- a/output/pdf_financials_xlsx/AURO.xlsx
+++ b/output/pdf_financials_xlsx/AURO.xlsx
@@ -1007,15 +1007,11 @@
       <c r="D23" s="3" t="n">
         <v>-4.448903</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>-0.932913</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-0.957581</v>
       </c>
     </row>
     <row r="24">
@@ -2080,7 +2076,7 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.026468</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -2102,7 +2098,7 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.026468</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -2190,7 +2186,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.050943</v>
+        <v>0.024475</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0.032232</v>
@@ -2262,7 +2258,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>0.013234</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -2284,7 +2280,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>0.013234</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2305,10 +2301,8 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.001448854103544788</v>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
@@ -2426,7 +2420,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0.013234</v>
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -2733,15 +2727,11 @@
       <c r="D99" s="3" t="n">
         <v>-4.448903</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-0.932913</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.957581</v>
       </c>
     </row>
     <row r="100">
@@ -2886,16 +2876,16 @@
         <v>0.0673</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-9.3e-05</v>
+        <v>-0.059928</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.377174</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.280855</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>0.309206</v>
       </c>
     </row>
     <row r="107">
@@ -6096,7 +6086,11 @@
           <t>Current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.026468</v>
       </c>
@@ -6180,7 +6174,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.013234</v>
       </c>
@@ -6422,7 +6420,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6754,7 +6756,11 @@
           <t>Changes in non-cash operating working capital 14</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -7738,7 +7744,11 @@
           <t>Changes in non-cash operating working capital 13</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
